--- a/excel/output_stats_sfvv/3mm/PerSubgraphStats.xlsx
+++ b/excel/output_stats_sfvv/3mm/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,10 +1481,10 @@
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>344.216</v>
+        <v>336.12</v>
       </c>
       <c r="O22" t="n">
-        <v>346.25</v>
+        <v>338.16</v>
       </c>
     </row>
     <row r="23">
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>344.215</v>
+        <v>336.12</v>
       </c>
       <c r="O23" t="n">
-        <v>352.29</v>
+        <v>340.97</v>
       </c>
     </row>
     <row r="24">
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>0.644172</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4.555</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.141421</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9342</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>783091000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3566980000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3269480000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>13665000000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>3000000000</v>
@@ -1575,10 +1575,10 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>341.511</v>
+        <v>338.405</v>
       </c>
       <c r="O24" t="n">
-        <v>351.42</v>
+        <v>340.07</v>
       </c>
     </row>
     <row r="25">
@@ -1586,34 +1586,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>0.493645</v>
+        <v>0.644172</v>
       </c>
       <c r="D25" t="n">
-        <v>2.76073</v>
+        <v>4.555</v>
       </c>
       <c r="E25" t="n">
-        <v>0.17881</v>
+        <v>0.141421</v>
       </c>
       <c r="F25" t="n">
-        <v>1.36282</v>
+        <v>2.9342</v>
       </c>
       <c r="G25" t="n">
-        <v>783188000</v>
+        <v>783091000</v>
       </c>
       <c r="H25" t="n">
-        <v>2162170000</v>
+        <v>3566980000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1981800000</v>
+        <v>3269480000</v>
       </c>
       <c r="K25" t="n">
-        <v>8282180000</v>
+        <v>13665000000</v>
       </c>
       <c r="L25" t="n">
         <v>3000000000</v>
@@ -1622,10 +1622,10 @@
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>344.716</v>
+        <v>338.405</v>
       </c>
       <c r="O25" t="n">
-        <v>350.92</v>
+        <v>346.27</v>
       </c>
     </row>
     <row r="26">
@@ -1633,34 +1633,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>2.43417e-09</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.243417</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2.43417e-17</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>600000000</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>3000000000</v>
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.151</v>
+        <v>344.716</v>
       </c>
       <c r="O26" t="n">
-        <v>350.2</v>
+        <v>345.33</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>8.717299999999999e-09</v>
+        <v>0.493645</v>
       </c>
       <c r="D27" t="n">
-        <v>3.33333e-08</v>
+        <v>2.76073</v>
       </c>
       <c r="E27" t="n">
-        <v>0.261519</v>
+        <v>0.17881</v>
       </c>
       <c r="F27" t="n">
-        <v>2.90577e-16</v>
+        <v>1.36282</v>
       </c>
       <c r="G27" t="n">
-        <v>930000000</v>
+        <v>783188000</v>
       </c>
       <c r="H27" t="n">
-        <v>31</v>
+        <v>2162170000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>1981800000</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>8282180000</v>
       </c>
       <c r="L27" t="n">
         <v>3000000000</v>
@@ -1716,10 +1716,10 @@
         <v>0.6</v>
       </c>
       <c r="N27" t="n">
-        <v>350.15</v>
+        <v>344.716</v>
       </c>
       <c r="O27" t="n">
-        <v>350.18</v>
+        <v>350.92</v>
       </c>
     </row>
     <row r="28">
@@ -1727,34 +1727,34 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>4.76522e-10</v>
+        <v>2.43417e-09</v>
       </c>
       <c r="D28" t="n">
-        <v>2e-09</v>
+        <v>1e-08</v>
       </c>
       <c r="E28" t="n">
-        <v>0.238261</v>
+        <v>0.243417</v>
       </c>
       <c r="F28" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>2.43417e-17</v>
       </c>
       <c r="G28" t="n">
-        <v>500000000</v>
+        <v>600000000</v>
       </c>
       <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L28" t="n">
         <v>3000000000</v>
@@ -1763,10 +1763,10 @@
         <v>0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O28" t="n">
-        <v>350.17</v>
+        <v>350.2</v>
       </c>
     </row>
     <row r="29">
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>4.76522e-10</v>
+        <v>8.717299999999999e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>2e-09</v>
+        <v>3.33333e-08</v>
       </c>
       <c r="E29" t="n">
-        <v>0.238261</v>
+        <v>0.261519</v>
       </c>
       <c r="F29" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>2.90577e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>500000000</v>
+        <v>930000000</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
         <v>3000000000</v>
@@ -1813,7 +1813,7 @@
         <v>350.15</v>
       </c>
       <c r="O29" t="n">
-        <v>350.17</v>
+        <v>350.18</v>
       </c>
     </row>
     <row r="30">
@@ -1821,34 +1821,34 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>6.24265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D30" t="n">
-        <v>2.33333e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E30" t="n">
-        <v>0.267542</v>
+        <v>0.238261</v>
       </c>
       <c r="F30" t="n">
-        <v>1.45662e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G30" t="n">
-        <v>857143000</v>
+        <v>500000000</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
         <v>3000000000</v>
@@ -1857,7 +1857,7 @@
         <v>0.6</v>
       </c>
       <c r="N30" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O30" t="n">
         <v>350.17</v>
@@ -1868,34 +1868,34 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>6.24265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D31" t="n">
-        <v>2.33333e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E31" t="n">
-        <v>0.267542</v>
+        <v>0.238261</v>
       </c>
       <c r="F31" t="n">
-        <v>1.45662e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G31" t="n">
-        <v>857143000</v>
+        <v>500000000</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>3000000000</v>
@@ -1904,7 +1904,7 @@
         <v>0.6</v>
       </c>
       <c r="N31" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O31" t="n">
         <v>350.17</v>
@@ -1915,34 +1915,34 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>1.48585e-09</v>
+        <v>6.24265e-10</v>
       </c>
       <c r="D32" t="n">
-        <v>5.66667e-09</v>
+        <v>2.33333e-09</v>
       </c>
       <c r="E32" t="n">
-        <v>0.262208</v>
+        <v>0.267542</v>
       </c>
       <c r="F32" t="n">
-        <v>8.419790000000001e-18</v>
+        <v>1.45662e-18</v>
       </c>
       <c r="G32" t="n">
-        <v>705882000</v>
+        <v>857143000</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
         <v>3000000000</v>
@@ -1951,7 +1951,7 @@
         <v>0.6</v>
       </c>
       <c r="N32" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O32" t="n">
         <v>350.17</v>
@@ -1962,34 +1962,34 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>1.21265e-10</v>
+        <v>6.24265e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>3.33333e-10</v>
+        <v>2.33333e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>0.363794</v>
+        <v>0.267542</v>
       </c>
       <c r="F33" t="n">
-        <v>4.04216e-20</v>
+        <v>1.45662e-18</v>
       </c>
       <c r="G33" t="n">
-        <v>3000000000</v>
+        <v>857143000</v>
       </c>
       <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
         <v>3000000000</v>
@@ -2001,6 +2001,100 @@
         <v>350.151</v>
       </c>
       <c r="O33" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.48585e-09</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.66667e-09</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.262208</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.419790000000001e-18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>705882000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>17</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O34" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.21265e-10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.33333e-10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.363794</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.04216e-20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O35" t="n">
         <v>350.22</v>
       </c>
     </row>
